--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 01:54:37</t>
+          <t>2026-06-27 04:13:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,17 +843,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -869,10 +869,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,261 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 04:13:14</t>
+          <t>2026-06-27 06:32:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-27 06:32:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -869,10 +869,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 06:32:20</t>
+          <t>2026-06-27 08:50:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 08:50:14</t>
+          <t>2026-06-27 11:06:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -869,208 +869,208 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 11:06:38</t>
+          <t>2026-06-27 13:21:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,498 +1097,1006 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
         <v>1.03</v>
       </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 11:06:38</t>
+          <t>2026-06-27 13:21:37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fk Siauliai</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TransINVEST Vilnius</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:21:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:45:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Panevezys</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FK Suduva</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:21:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>IA Akranes</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Fram</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-27 11:06:38</t>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:21:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -863,13 +863,13 @@
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,16 +881,16 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R2" t="n">
         <v>1.07</v>
@@ -905,7 +905,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 13:21:37</t>
+          <t>2026-06-27 15:35:48</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="O3" t="n">
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Q3" t="n">
         <v>1.33</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 13:21:37</t>
+          <t>2026-06-27 15:35:48</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="I4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.21</v>
@@ -1407,28 +1407,28 @@
         <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
         <v>30</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AB4" t="n">
         <v>36</v>
@@ -1437,13 +1437,13 @@
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG4" t="n">
         <v>27</v>
@@ -1458,13 +1458,13 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL4" t="n">
         <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
         <v>95</v>
@@ -1473,7 +1473,7 @@
         <v>7.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.4</v>
@@ -1482,10 +1482,10 @@
         <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
@@ -1494,73 +1494,73 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
         <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
         <v>5.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>4.5</v>
@@ -1572,13 +1572,13 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 13:21:37</t>
+          <t>2026-06-27 15:35:48</t>
         </is>
       </c>
     </row>
@@ -1619,52 +1619,52 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G5" t="n">
         <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I5" t="n">
         <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
         <v>1.76</v>
@@ -1673,112 +1673,112 @@
         <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 13:21:37</t>
+          <t>2026-06-27 15:35:48</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 13:21:37</t>
+          <t>2026-06-27 15:35:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -890,22 +890,22 @@
         <v>1.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R2" t="n">
         <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -1022,55 +1022,55 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
         <v>3.25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1365,67 +1365,67 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="I4" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
         <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
         <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
@@ -1443,37 +1443,37 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG4" t="n">
         <v>27</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
         <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.4</v>
@@ -1482,10 +1482,10 @@
         <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
@@ -1494,34 +1494,34 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
         <v>5.3</v>
@@ -1530,55 +1530,55 @@
         <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
         <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I5" t="n">
         <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.65</v>
@@ -1643,13 +1643,13 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
         <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
         <v>2.08</v>
@@ -1661,10 +1661,10 @@
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V5" t="n">
         <v>1.76</v>
@@ -1733,7 +1733,7 @@
         <v>3</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="AS5" t="n">
         <v>3.7</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>
@@ -1891,212 +1891,212 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 15:35:48</t>
+          <t>2026-06-27 17:48:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
         <v>4.6</v>
@@ -1649,7 +1649,7 @@
         <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
         <v>2.08</v>
@@ -1661,10 +1661,10 @@
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
         <v>1.76</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>
@@ -1903,13 +1903,13 @@
         <v>1.08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
         <v>1.08</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 17:48:42</t>
+          <t>2026-06-27 20:01:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>5.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="G5" t="n">
         <v>4.6</v>
@@ -1661,10 +1661,10 @@
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V5" t="n">
         <v>1.76</v>
@@ -1733,7 +1733,7 @@
         <v>3</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.4</v>
+        <v>3.3</v>
       </c>
       <c r="AS5" t="n">
         <v>3.7</v>
@@ -1781,68 +1781,68 @@
         <v>3.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 20:01:19</t>
+          <t>2026-06-27 22:13:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -893,10 +893,10 @@
         <v>1.23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
         <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
         <v>1.76</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-27 22:13:34</t>
+          <t>2026-06-28 00:25:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="I4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1389,55 +1389,55 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
         <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>970</v>
@@ -1446,16 +1446,16 @@
         <v>55</v>
       </c>
       <c r="AG4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AH4" t="n">
         <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK4" t="n">
         <v>80</v>
@@ -1467,70 +1467,70 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO4" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW4" t="n">
         <v>5.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5</v>
-      </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BH4" t="n">
         <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1542,43 +1542,43 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.9</v>
+        <v>2.28</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="BT4" t="n">
         <v>4.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.65</v>
@@ -1643,13 +1643,13 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
         <v>2.08</v>
@@ -1658,19 +1658,19 @@
         <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1682,13 +1682,13 @@
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>13.5</v>
@@ -1697,10 +1697,10 @@
         <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>24</v>
@@ -1709,76 +1709,76 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AK5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
         <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV5" t="n">
         <v>3.25</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AW5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG5" t="n">
         <v>3.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.25</v>
@@ -1796,31 +1796,31 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.94</v>
+        <v>4.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 00:25:49</t>
+          <t>2026-06-28 02:38:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>2.54</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
         <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -1111,157 +1111,157 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>2.42</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
         <v>1.03</v>
@@ -1273,68 +1273,68 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
@@ -1374,7 +1374,7 @@
         <v>1.65</v>
       </c>
       <c r="I4" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -1395,7 +1395,7 @@
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.69</v>
@@ -1410,10 +1410,10 @@
         <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="W4" t="n">
         <v>1.2</v>
@@ -1473,97 +1473,97 @@
         <v>11</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" t="n">
         <v>5.8</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
         <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="BN4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU4" t="n">
         <v>3.6</v>
@@ -1578,7 +1578,7 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.2</v>
+        <v>2.76</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -1619,91 +1619,91 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
         <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
         <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
         <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF5" t="n">
         <v>32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>34</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
@@ -1718,16 +1718,16 @@
         <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AQ5" t="n">
         <v>3.05</v>
@@ -1739,10 +1739,10 @@
         <v>3.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="AV5" t="n">
         <v>3.25</v>
@@ -1751,16 +1751,16 @@
         <v>3.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AY5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>3.55</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB5" t="n">
         <v>4.1</v>
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
         <v>3.7</v>
@@ -1784,40 +1784,40 @@
         <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU5" t="n">
         <v>3.45</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 02:38:07</t>
+          <t>2026-06-28 04:50:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -860,97 +860,97 @@
         <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
         <v>21</v>
       </c>
       <c r="AB2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
         <v>65</v>
@@ -959,10 +959,10 @@
         <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
         <v>1.01</v>
@@ -971,7 +971,7 @@
         <v>8.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AS2" t="n">
         <v>1.01</v>
@@ -983,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW2" t="n">
         <v>1.01</v>
@@ -1016,25 +1016,25 @@
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
         <v>5.6</v>
       </c>
-      <c r="BI2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BN2" t="n">
         <v>12</v>
@@ -1046,31 +1046,31 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="BT2" t="n">
         <v>5.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BV2" t="n">
         <v>13.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -1111,184 +1111,184 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.32</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="X3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
         <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="I4" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
@@ -1443,10 +1443,10 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AG4" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>970</v>
@@ -1455,130 +1455,130 @@
         <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AO4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AP4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="AW4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX4" t="n">
         <v>5</v>
       </c>
-      <c r="AS4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>8</v>
       </c>
-      <c r="BD4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BU4" t="n">
         <v>3.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -1619,82 +1619,82 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="I5" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
         <v>32</v>
@@ -1703,146 +1703,146 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ5" t="n">
         <v>95</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
         <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
         <v>70</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA5" t="n">
         <v>3.25</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="BB5" t="n">
         <v>3.35</v>
       </c>
-      <c r="AU5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
         <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>8</v>
-      </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 04:50:33</t>
+          <t>2026-06-28 07:03:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -860,25 +860,25 @@
         <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
         <v>4.7</v>
@@ -887,13 +887,13 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
         <v>2.66</v>
@@ -905,10 +905,10 @@
         <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -920,7 +920,7 @@
         <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB2" t="n">
         <v>25</v>
@@ -929,7 +929,7 @@
         <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>970</v>
@@ -944,7 +944,7 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
         <v>130</v>
@@ -1019,25 +1019,25 @@
         <v>6.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="BN2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
         <v>6.2</v>
@@ -1046,22 +1046,22 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.42</v>
+        <v>1.81</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
         <v>6.2</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
         <v>2.3</v>
@@ -1120,7 +1120,7 @@
         <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
@@ -1156,10 +1156,10 @@
         <v>1.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.77</v>
@@ -1186,7 +1186,7 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1219,34 +1219,34 @@
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR3" t="n">
         <v>3.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
         <v>3.55</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ3" t="n">
         <v>3.65</v>
@@ -1258,37 +1258,37 @@
         <v>3.85</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
         <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
         <v>7.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -1365,67 +1365,67 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
         <v>4.1</v>
       </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="T4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>970</v>
@@ -1455,19 +1455,19 @@
         <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
         <v>970</v>
@@ -1476,109 +1476,109 @@
         <v>5.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW4" t="n">
         <v>6</v>
       </c>
-      <c r="AU4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV4" t="n">
+      <c r="AX4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BT4" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BU4" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -1619,37 +1619,37 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
         <v>2.08</v>
@@ -1658,19 +1658,19 @@
         <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.93</v>
       </c>
       <c r="U5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V5" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1691,7 +1691,7 @@
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
@@ -1703,7 +1703,7 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
         <v>50</v>
@@ -1718,7 +1718,7 @@
         <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
         <v>70</v>
@@ -1727,58 +1727,58 @@
         <v>970</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY5" t="n">
         <v>4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AZ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BB5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
         <v>3.25</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>5.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 07:03:39</t>
+          <t>2026-06-28 09:15:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G2" t="n">
         <v>5.7</v>
@@ -869,13 +869,13 @@
         <v>1.75</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -884,25 +884,25 @@
         <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
         <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
         <v>2.32</v>
@@ -935,7 +935,7 @@
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AG2" t="n">
         <v>22</v>
@@ -947,19 +947,19 @@
         <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AK2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN2" t="n">
         <v>65</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>60</v>
       </c>
       <c r="AO2" t="n">
         <v>9.800000000000001</v>
@@ -971,7 +971,7 @@
         <v>8.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
         <v>1.01</v>
@@ -983,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
         <v>1.01</v>
@@ -1019,22 +1019,22 @@
         <v>6.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,31 +1046,31 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.29</v>
+        <v>3</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
@@ -1126,7 +1126,7 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.37</v>
@@ -1144,7 +1144,7 @@
         <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.29</v>
@@ -1162,7 +1162,7 @@
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1276,7 +1276,7 @@
         <v>7.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1392,19 +1392,19 @@
         <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
@@ -1413,10 +1413,10 @@
         <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1455,7 +1455,7 @@
         <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="n">
         <v>50</v>
@@ -1464,7 +1464,7 @@
         <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
         <v>46</v>
@@ -1473,10 +1473,10 @@
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1485,43 +1485,43 @@
         <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
         <v>9.6</v>
@@ -1536,16 +1536,16 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BO4" t="n">
         <v>6</v>
@@ -1560,25 +1560,25 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
@@ -1637,40 +1637,40 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
         <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1682,22 +1682,22 @@
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1709,10 +1709,10 @@
         <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AK5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AL5" t="n">
         <v>75</v>
@@ -1721,128 +1721,128 @@
         <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
         <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
         <v>3.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BA5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO5" t="n">
         <v>4</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>
@@ -1909,10 +1909,10 @@
         <v>1.07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 09:15:53</t>
+          <t>2026-06-28 11:26:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,88 +857,88 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
@@ -947,25 +947,25 @@
         <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>8.6</v>
@@ -974,70 +974,70 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="AV2" t="n">
         <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.54</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO2" t="n">
         <v>6.2</v>
@@ -1046,31 +1046,31 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.91</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.37</v>
@@ -1135,25 +1135,25 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
         <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
@@ -1219,16 +1219,16 @@
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>3.85</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>3.3</v>
@@ -1237,46 +1237,46 @@
         <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1288,53 +1288,53 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.26</v>
+        <v>2.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1410,10 +1410,10 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
         <v>1.33</v>
@@ -1431,7 +1431,7 @@
         <v>970</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
@@ -1473,10 +1473,10 @@
         <v>970</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1485,43 +1485,43 @@
         <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BB4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC4" t="n">
         <v>8</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BD4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF4" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
         <v>9.6</v>
@@ -1542,10 +1542,10 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
         <v>6</v>
@@ -1554,22 +1554,22 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW4" t="n">
         <v>6.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1643,46 +1643,46 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
         <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
@@ -1694,7 +1694,7 @@
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
         <v>42</v>
@@ -1709,140 +1709,140 @@
         <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AK5" t="n">
         <v>80</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM5" t="n">
         <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
         <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
         <v>3.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
         <v>4.5</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>7.2</v>
       </c>
-      <c r="BN5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>6</v>
-      </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="O6" t="n">
         <v>1.08</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 11:26:33</t>
+          <t>2026-06-28 13:36:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
         <v>1.52</v>
@@ -869,40 +869,40 @@
         <v>1.56</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K2" t="n">
         <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>2.78</v>
@@ -914,7 +914,7 @@
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
         <v>12.5</v>
@@ -935,10 +935,10 @@
         <v>17.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AG2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH2" t="n">
         <v>970</v>
@@ -947,28 +947,28 @@
         <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="n">
         <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
         <v>8.800000000000001</v>
@@ -977,76 +977,76 @@
         <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AV2" t="n">
         <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BG2" t="n">
         <v>5.1</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1055,22 +1055,22 @@
         <v>10</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
@@ -1153,7 +1153,7 @@
         <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
@@ -1219,40 +1219,40 @@
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AQ3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX3" t="n">
         <v>3.85</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.65</v>
       </c>
       <c r="AY3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
         <v>4.4</v>
@@ -1261,22 +1261,22 @@
         <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.04</v>
+        <v>1.26</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -1371,10 +1371,10 @@
         <v>3.95</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1485,10 +1485,10 @@
         <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV4" t="n">
         <v>5.2</v>
@@ -1506,7 +1506,7 @@
         <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BB4" t="n">
         <v>8.4</v>
@@ -1527,7 +1527,7 @@
         <v>9.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
         <v>3</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="BT4" t="n">
         <v>5.2</v>
@@ -1578,7 +1578,7 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1625,16 @@
         <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="I5" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1643,13 +1643,13 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
@@ -1658,7 +1658,7 @@
         <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
         <v>1.92</v>
@@ -1667,7 +1667,7 @@
         <v>1.84</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W5" t="n">
         <v>1.23</v>
@@ -1679,7 +1679,7 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
         <v>22</v>
@@ -1727,58 +1727,58 @@
         <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.45</v>
@@ -1820,13 +1820,13 @@
         <v>4.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,261 +1842,1023 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 13:36:45</t>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Argentinian Primera C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sportivo Barracas</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Club Lujan</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:45:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aegir</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:45:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>16:15:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>IA Akranes</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Fram</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.63</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O8" t="n">
         <v>1.08</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:45:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Democrata GV</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ivinhema FC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>110</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I9" t="n">
+        <v>110</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-28 13:36:45</t>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:45:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -875,46 +875,46 @@
         <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
         <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>2.78</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
         <v>12.5</v>
@@ -923,7 +923,7 @@
         <v>16</v>
       </c>
       <c r="AB2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AC2" t="n">
         <v>12.5</v>
@@ -932,7 +932,7 @@
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AF2" t="n">
         <v>60</v>
@@ -962,61 +962,61 @@
         <v>85</v>
       </c>
       <c r="AO2" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AV2" t="n">
         <v>8</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="n">
         <v>6.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
         <v>2.3</v>
@@ -1129,7 +1129,7 @@
         <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1273,10 +1273,10 @@
         <v>4.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.26</v>
+        <v>2.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,13 +1312,13 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1664,7 +1664,7 @@
         <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
         <v>1.98</v>
@@ -1748,7 +1748,7 @@
         <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
         <v>5.2</v>
@@ -1760,7 +1760,7 @@
         <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB5" t="n">
         <v>5.8</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="J6" t="n">
         <v>2.62</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
         <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
         <v>1.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="R6" t="n">
         <v>1.14</v>
@@ -1915,25 +1915,25 @@
         <v>6.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
         <v>65</v>
@@ -1981,58 +1981,58 @@
         <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="n">
         <v>2.7</v>
@@ -2044,59 +2044,59 @@
         <v>13.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP6" t="n">
         <v>38</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT6" t="n">
         <v>6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV6" t="n">
         <v>30</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="I7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="K7" t="n">
         <v>7.8</v>
@@ -2151,7 +2151,7 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.1</v>
@@ -2166,25 +2166,25 @@
         <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T7" t="n">
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="X7" t="n">
         <v>60</v>
       </c>
       <c r="Y7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Z7" t="n">
         <v>120</v>
@@ -2193,19 +2193,19 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AD7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AE7" t="n">
         <v>130</v>
       </c>
       <c r="AF7" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
         <v>16</v>
@@ -2217,10 +2217,10 @@
         <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AK7" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -2235,122 +2235,122 @@
         <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="n">
         <v>6.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>
@@ -2635,40 +2635,40 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.02</v>
       </c>
-      <c r="G9" t="n">
-        <v>110</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I9" t="n">
-        <v>110</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K9" t="n">
-        <v>950</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>1.25</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2743,58 +2743,58 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-28 15:45:53</t>
+          <t>2026-06-28 17:53:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,40 +857,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="I2" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
@@ -899,145 +899,145 @@
         <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AX2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG2" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.4</v>
       </c>
       <c r="BH2" t="n">
         <v>6.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BO2" t="n">
         <v>6.6</v>
@@ -1052,25 +1052,25 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BU2" t="n">
         <v>3.45</v>
       </c>
       <c r="BV2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
         <v>2.3</v>
@@ -1126,7 +1126,7 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
@@ -1135,7 +1135,7 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
@@ -1153,7 +1153,7 @@
         <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
@@ -1165,115 +1165,115 @@
         <v>1.78</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AV3" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AY3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="BH3" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BI3" t="n">
         <v>2.58</v>
@@ -1282,16 +1282,16 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
         <v>3.8</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -1395,13 +1395,13 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
         <v>1.81</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1410,19 +1410,19 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W4" t="n">
         <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z4" t="n">
         <v>970</v>
@@ -1443,40 +1443,40 @@
         <v>970</v>
       </c>
       <c r="AF4" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1488,13 +1488,13 @@
         <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1506,22 +1506,22 @@
         <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD4" t="n">
         <v>8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BE4" t="n">
         <v>8.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG4" t="n">
         <v>9.6</v>
@@ -1530,7 +1530,7 @@
         <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="I5" t="n">
         <v>2.02</v>
@@ -1634,7 +1634,7 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1664,121 +1664,121 @@
         <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
         <v>1.98</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AR5" t="n">
         <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY5" t="n">
         <v>5.2</v>
       </c>
-      <c r="AY5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
         <v>3.45</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>2.62</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.62</v>
@@ -1903,7 +1903,7 @@
         <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
         <v>2.76</v>
@@ -1927,112 +1927,112 @@
         <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
         <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
         <v>75</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH6" t="n">
         <v>2.7</v>
@@ -2041,16 +2041,16 @@
         <v>2.08</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
@@ -2068,19 +2068,19 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
         <v>6</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BV6" t="n">
         <v>30</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
         <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K7" t="n">
         <v>7.8</v>
@@ -2166,13 +2166,13 @@
         <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="T7" t="n">
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -2181,10 +2181,10 @@
         <v>3.8</v>
       </c>
       <c r="X7" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="Y7" t="n">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="Z7" t="n">
         <v>120</v>
@@ -2199,7 +2199,7 @@
         <v>24</v>
       </c>
       <c r="AD7" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AE7" t="n">
         <v>130</v>
@@ -2211,10 +2211,10 @@
         <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AJ7" t="n">
         <v>17</v>
@@ -2223,31 +2223,31 @@
         <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="AN7" t="n">
         <v>3.35</v>
       </c>
       <c r="AO7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>13.5</v>
@@ -2256,37 +2256,37 @@
         <v>24</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>17</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="n">
         <v>6.4</v>
@@ -2307,10 +2307,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
         <v>7.6</v>
@@ -2328,7 +2328,7 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
         <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I8" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="J8" t="n">
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>1.18</v>
@@ -2405,7 +2405,7 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.11</v>
@@ -2414,16 +2414,16 @@
         <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="T8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U8" t="n">
         <v>3.25</v>
@@ -2435,28 +2435,28 @@
         <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
         <v>34</v>
@@ -2468,79 +2468,79 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
         <v>12.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
         <v>32</v>
       </c>
       <c r="AQ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW8" t="n">
         <v>7</v>
       </c>
-      <c r="AR8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AX8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.8</v>
       </c>
       <c r="BA8" t="n">
         <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
         <v>5.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>
@@ -2635,175 +2635,175 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>3.55</v>
+        <v>1.69</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.24</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>2.46</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
@@ -2815,25 +2815,25 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
         <v>1.01</v>
@@ -2851,14 +2851,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA9" t="n">
         <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-28 17:53:37</t>
+          <t>2026-06-28 20:00:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -869,31 +869,31 @@
         <v>1.49</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
         <v>5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
         <v>2.44</v>
@@ -902,10 +902,10 @@
         <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="W2" t="n">
         <v>1.14</v>
@@ -914,7 +914,7 @@
         <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
         <v>11</v>
@@ -956,7 +956,7 @@
         <v>190</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
         <v>90</v>
@@ -968,10 +968,10 @@
         <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS2" t="n">
         <v>11.5</v>
@@ -983,34 +983,34 @@
         <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY2" t="n">
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H3" t="n">
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
@@ -1147,16 +1147,16 @@
         <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V3" t="n">
         <v>1.33</v>
@@ -1228,7 +1228,7 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
         <v>4.9</v>
@@ -1240,7 +1240,7 @@
         <v>6.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>6.4</v>
@@ -1264,16 +1264,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
         <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BI3" t="n">
         <v>2.58</v>
@@ -1282,7 +1282,7 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>3.95</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1413,10 +1413,10 @@
         <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="I5" t="n">
         <v>2.02</v>
@@ -1634,7 +1634,7 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1670,7 +1670,7 @@
         <v>1.98</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1736,49 +1736,49 @@
         <v>7.4</v>
       </c>
       <c r="AS5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT5" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
         <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
         <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
         <v>3.45</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -1879,19 +1879,19 @@
         <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
         <v>2.62</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
@@ -1921,7 +1921,7 @@
         <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
@@ -2056,7 +2056,7 @@
         <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
         <v>38</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -2139,10 +2139,10 @@
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.17</v>
@@ -2223,7 +2223,7 @@
         <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
         <v>260</v>
@@ -2235,16 +2235,16 @@
         <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
@@ -2256,7 +2256,7 @@
         <v>24</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -2268,7 +2268,7 @@
         <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
         <v>10.5</v>
@@ -2280,7 +2280,7 @@
         <v>17</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
         <v>2.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
         <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -2513,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="AY8" t="n">
         <v>6.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.69</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
         <v>8.800000000000001</v>
@@ -2659,19 +2659,19 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
         <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
         <v>3.8</v>
@@ -2713,7 +2713,7 @@
         <v>170</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2743,58 +2743,58 @@
         <v>270</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD9" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.35</v>
@@ -2806,13 +2806,13 @@
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN9" t="n">
         <v>4.1</v>
@@ -2824,41 +2824,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
         <v>34</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT9" t="n">
         <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>26</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-28 20:00:34</t>
+          <t>2026-06-28 22:07:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -860,7 +860,7 @@
         <v>6.8</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H2" t="n">
         <v>1.45</v>
@@ -869,7 +869,7 @@
         <v>1.49</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K2" t="n">
         <v>5.6</v>
@@ -881,52 +881,52 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
         <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="W2" t="n">
         <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
         <v>13.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
         <v>10.5</v>
@@ -941,28 +941,28 @@
         <v>30</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>30</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AK2" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AL2" t="n">
         <v>190</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AO2" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
@@ -971,55 +971,55 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>11.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
         <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="AY2" t="n">
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BD2" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BI2" t="n">
         <v>4.4</v>
@@ -1028,7 +1028,7 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1055,10 +1055,10 @@
         <v>10.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV2" t="n">
         <v>8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
@@ -1141,7 +1141,7 @@
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
         <v>2.06</v>
@@ -1195,7 +1195,7 @@
         <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1216,7 +1216,7 @@
         <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>6.2</v>
@@ -1228,19 +1228,19 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AX3" t="n">
         <v>6.4</v>
@@ -1249,31 +1249,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="BB3" t="n">
         <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="BF3" t="n">
         <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI3" t="n">
         <v>2.58</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I4" t="n">
         <v>2.26</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1404,13 +1404,13 @@
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
         <v>1.79</v>
@@ -1434,7 +1434,7 @@
         <v>22</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1473,10 +1473,10 @@
         <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -1485,49 +1485,49 @@
         <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV4" t="n">
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX4" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AY4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4" t="n">
         <v>9.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI4" t="n">
         <v>3.05</v>
@@ -1542,10 +1542,10 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
         <v>6</v>
@@ -1554,31 +1554,31 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BT4" t="n">
         <v>5.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
         <v>16</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="I5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
         <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
         <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
         <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
         <v>15</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>14</v>
@@ -1694,7 +1694,7 @@
         <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
@@ -1721,106 +1721,106 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
         <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.8</v>
+        <v>2.38</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>1.89</v>
       </c>
       <c r="BT5" t="n">
         <v>4.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.54</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.62</v>
       </c>
       <c r="K6" t="n">
         <v>2.98</v>
       </c>
       <c r="L6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>6.8</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
         <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
         <v>18.5</v>
@@ -1939,10 +1939,10 @@
         <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
         <v>17</v>
@@ -1951,13 +1951,13 @@
         <v>130</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
         <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1966,10 +1966,10 @@
         <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
@@ -1978,125 +1978,125 @@
         <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK6" t="n">
         <v>4.9</v>
       </c>
-      <c r="BA6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6</v>
-      </c>
       <c r="BU6" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
@@ -2142,7 +2142,7 @@
         <v>6.4</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.17</v>
@@ -2166,7 +2166,7 @@
         <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="T7" t="n">
         <v>1.64</v>
@@ -2178,7 +2178,7 @@
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="X7" t="n">
         <v>240</v>
@@ -2235,10 +2235,10 @@
         <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AR7" t="n">
         <v>8.6</v>
@@ -2268,7 +2268,7 @@
         <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
         <v>10.5</v>
@@ -2280,10 +2280,10 @@
         <v>17</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
@@ -2298,59 +2298,59 @@
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>7.4</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.18</v>
@@ -2414,13 +2414,13 @@
         <v>3.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="T8" t="n">
         <v>1.39</v>
@@ -2480,7 +2480,7 @@
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>12.5</v>
@@ -2489,16 +2489,16 @@
         <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
@@ -2513,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
         <v>6.2</v>
@@ -2525,7 +2525,7 @@
         <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BC8" t="n">
         <v>7.4</v>
@@ -2540,7 +2540,7 @@
         <v>9.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH8" t="n">
         <v>5.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
         <v>8.800000000000001</v>
@@ -2653,16 +2653,16 @@
         <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
         <v>1.73</v>
@@ -2671,16 +2671,16 @@
         <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
         <v>1.12</v>
@@ -2689,7 +2689,7 @@
         <v>2.46</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -2719,7 +2719,7 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="n">
         <v>160</v>
@@ -2731,134 +2731,134 @@
         <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.5</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>3.85</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-28 22:07:36</t>
+          <t>2026-06-29 00:14:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,130 +857,130 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.45</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.49</v>
-      </c>
       <c r="J2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
         <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC2" t="n">
         <v>13.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AK2" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="AL2" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
         <v>11.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.199999999999999</v>
@@ -989,88 +989,88 @@
         <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AY2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BD2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE2" t="n">
         <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BG2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH2" t="n">
         <v>5</v>
       </c>
-      <c r="BH2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BI2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BV2" t="n">
         <v>8</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1111,52 +1111,52 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
         <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
         <v>1.33</v>
@@ -1165,46 +1165,46 @@
         <v>1.78</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1219,79 +1219,79 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.25</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.7</v>
+        <v>32</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.7</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.2</v>
+        <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.56</v>
+        <v>34</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI3" t="n">
         <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.66</v>
+        <v>2.64</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BO3" t="n">
         <v>3.8</v>
@@ -1300,41 +1300,41 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.68</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.76</v>
+        <v>2.64</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.58</v>
+        <v>2.44</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.5</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AB4" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.6</v>
@@ -1440,25 +1440,25 @@
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AF4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>500</v>
       </c>
-      <c r="AG4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>900</v>
-      </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
@@ -1470,82 +1470,82 @@
         <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BG4" t="n">
         <v>9.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN4" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
         <v>6</v>
@@ -1554,31 +1554,31 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
         <v>8</v>
       </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BT4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU4" t="n">
         <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1622,91 +1622,91 @@
         <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H5" t="n">
         <v>1.85</v>
       </c>
       <c r="I5" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
         <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
         <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
         <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
@@ -1721,128 +1721,128 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>85</v>
+        <v>16.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -1873,34 +1873,34 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="K6" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
         <v>1.35</v>
@@ -1915,61 +1915,61 @@
         <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
@@ -1978,125 +1978,125 @@
         <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.65</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.65</v>
+        <v>1.69</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>1.88</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>1.72</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.8</v>
+        <v>1.71</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>1.88</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.2</v>
+        <v>1.82</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.5</v>
+        <v>1.86</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>1.89</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.2</v>
+        <v>1.89</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="J7" t="n">
         <v>6.4</v>
       </c>
       <c r="K7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
@@ -2157,28 +2157,28 @@
         <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
         <v>240</v>
@@ -2190,25 +2190,25 @@
         <v>120</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB7" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AD7" t="n">
         <v>120</v>
       </c>
       <c r="AE7" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>44</v>
@@ -2217,85 +2217,85 @@
         <v>320</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
         <v>260</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AO7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BG7" t="n">
         <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
         <v>8.199999999999999</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
         <v>4.7</v>
@@ -2313,44 +2313,44 @@
         <v>4</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ7" t="n">
         <v>5.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU7" t="n">
         <v>10.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CA7" t="n">
         <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -2381,55 +2381,55 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.2</v>
       </c>
-      <c r="K8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1.11</v>
       </c>
       <c r="P8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T8" t="n">
         <v>1.39</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
         <v>1.52</v>
@@ -2438,7 +2438,7 @@
         <v>500</v>
       </c>
       <c r="Y8" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2450,22 +2450,22 @@
         <v>500</v>
       </c>
       <c r="AC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>970</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
@@ -2474,7 +2474,7 @@
         <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2483,100 +2483,100 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
         <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
         <v>9.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BI8" t="n">
         <v>5.1</v>
       </c>
       <c r="BJ8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BK8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>8</v>
-      </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>
@@ -2635,100 +2635,100 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="G9" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
         <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AE9" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
         <v>75</v>
       </c>
       <c r="AI9" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2737,22 +2737,22 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
         <v>4.2</v>
@@ -2761,10 +2761,10 @@
         <v>5.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
         <v>4.2</v>
@@ -2773,92 +2773,92 @@
         <v>6.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 00:14:23</t>
+          <t>2026-06-29 02:21:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -860,13 +860,13 @@
         <v>7.4</v>
       </c>
       <c r="G2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J2" t="n">
         <v>5.5</v>
@@ -884,28 +884,28 @@
         <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="W2" t="n">
         <v>1.13</v>
@@ -926,10 +926,10 @@
         <v>40</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
@@ -938,7 +938,7 @@
         <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -950,28 +950,28 @@
         <v>250</v>
       </c>
       <c r="AK2" t="n">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AL2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO2" t="n">
         <v>5.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>11.5</v>
@@ -980,7 +980,7 @@
         <v>32</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>9.199999999999999</v>
@@ -989,22 +989,22 @@
         <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AY2" t="n">
         <v>26</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BD2" t="n">
         <v>46</v>
@@ -1016,13 +1016,13 @@
         <v>50</v>
       </c>
       <c r="BG2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI2" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1040,16 +1040,16 @@
         <v>11</v>
       </c>
       <c r="BO2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BR2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
         <v>12.5</v>
@@ -1061,7 +1061,7 @@
         <v>3.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW2" t="n">
         <v>7</v>
@@ -1070,7 +1070,7 @@
         <v>19</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -1111,88 +1111,88 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.78</v>
-      </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
         <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
@@ -1207,22 +1207,22 @@
         <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -1234,7 +1234,7 @@
         <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
         <v>12</v>
@@ -1246,7 +1246,7 @@
         <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
@@ -1258,83 +1258,83 @@
         <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
         <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.64</v>
+        <v>1.74</v>
       </c>
       <c r="BN3" t="n">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.64</v>
+        <v>3.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.44</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H4" t="n">
         <v>2.1</v>
       </c>
       <c r="I4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -1392,37 +1392,37 @@
         <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
         <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
         <v>17.5</v>
@@ -1434,13 +1434,13 @@
         <v>19.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>48</v>
@@ -1449,7 +1449,7 @@
         <v>18.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>46</v>
@@ -1467,16 +1467,16 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
         <v>11.5</v>
@@ -1485,25 +1485,25 @@
         <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>25</v>
@@ -1515,34 +1515,34 @@
         <v>29</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
         <v>23</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
@@ -1551,34 +1551,34 @@
         <v>6</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU4" t="n">
         <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="I5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1691,7 +1691,7 @@
         <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
@@ -1733,28 +1733,28 @@
         <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
         <v>16</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW5" t="n">
         <v>16</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
         <v>17</v>
@@ -1763,61 +1763,61 @@
         <v>30</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI5" t="n">
         <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU5" t="n">
         <v>3.75</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
         <v>10.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="I6" t="n">
-        <v>7.2</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
         <v>2.44</v>
@@ -1891,7 +1891,7 @@
         <v>2.72</v>
       </c>
       <c r="L6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
         <v>1.13</v>
@@ -1900,46 +1900,46 @@
         <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P6" t="n">
         <v>1.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
         <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC6" t="n">
         <v>42</v>
@@ -1954,85 +1954,85 @@
         <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
         <v>500</v>
       </c>
       <c r="AI6" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>500</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.7</v>
+        <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.69</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AS6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.88</v>
       </c>
-      <c r="AT6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BF6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BG6" t="n">
         <v>1.86</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.9</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
         <v>1.32</v>
       </c>
       <c r="H7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I7" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.19</v>
@@ -2151,70 +2151,70 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.1</v>
       </c>
       <c r="P7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
         <v>1.31</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="T7" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
         <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="Y7" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="Z7" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AA7" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AB7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC7" t="n">
         <v>18.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AE7" t="n">
         <v>260</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
         <v>13.5</v>
@@ -2223,70 +2223,70 @@
         <v>14</v>
       </c>
       <c r="AL7" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AM7" t="n">
         <v>260</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7</v>
-      </c>
       <c r="BD7" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BG7" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BH7" t="n">
         <v>6.2</v>
@@ -2304,13 +2304,13 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
         <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
         <v>7.4</v>
@@ -2322,25 +2322,25 @@
         <v>16.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BU7" t="n">
         <v>10.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10</v>
       </c>
       <c r="BZ7" t="n">
         <v>7.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
         <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.21</v>
@@ -2405,142 +2405,142 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1.11</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
         <v>1.35</v>
       </c>
       <c r="R8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="U8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="Y8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
         <v>500</v>
       </c>
       <c r="AB8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE8" t="n">
         <v>500</v>
       </c>
-      <c r="AC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>24</v>
-      </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AG8" t="n">
         <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK8" t="n">
         <v>500</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="AU8" t="n">
         <v>10.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BB8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="n">
         <v>5.8</v>
@@ -2561,16 +2561,16 @@
         <v>6.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
@@ -2588,7 +2588,7 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2597,14 +2597,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA8" t="n">
         <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="H9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
@@ -2677,7 +2677,7 @@
         <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
         <v>1.68</v>
@@ -2686,179 +2686,179 @@
         <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN9" t="n">
         <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.94</v>
+        <v>40</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BR9" t="n">
         <v>34</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BT9" t="n">
         <v>12</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BZ9" t="n">
         <v>24</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 02:21:25</t>
+          <t>2026-06-29 04:28:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H2" t="n">
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.26</v>
@@ -884,25 +884,25 @@
         <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>3.15</v>
@@ -914,22 +914,22 @@
         <v>27</v>
       </c>
       <c r="Y2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AA2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
@@ -941,31 +941,31 @@
         <v>29</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
         <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AK2" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AL2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
         <v>90</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>10.5</v>
@@ -980,13 +980,13 @@
         <v>32</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX2" t="n">
         <v>55</v>
@@ -995,16 +995,16 @@
         <v>26</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BD2" t="n">
         <v>46</v>
@@ -1016,61 +1016,61 @@
         <v>50</v>
       </c>
       <c r="BG2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BH2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BI2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
         <v>11</v>
       </c>
       <c r="BO2" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BW2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
@@ -1135,40 +1135,40 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
         <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
         <v>36</v>
@@ -1177,13 +1177,13 @@
         <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>120</v>
@@ -1195,10 +1195,10 @@
         <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>360</v>
+        <v>260</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
@@ -1222,10 +1222,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
         <v>28</v>
@@ -1234,7 +1234,7 @@
         <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
         <v>12</v>
@@ -1243,52 +1243,52 @@
         <v>32</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
         <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BF3" t="n">
         <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="BN3" t="n">
         <v>4.8</v>
@@ -1300,16 +1300,16 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BT3" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>7</v>
       </c>
       <c r="BU3" t="n">
         <v>6</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.4</v>
+        <v>1.82</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1395,109 +1395,109 @@
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.84</v>
       </c>
       <c r="W4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
         <v>30</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>9.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="AO4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR4" t="n">
         <v>12</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT4" t="n">
         <v>14</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW4" t="n">
         <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>13</v>
@@ -1506,7 +1506,7 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB4" t="n">
         <v>46</v>
@@ -1527,7 +1527,7 @@
         <v>11.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BI4" t="n">
         <v>3.15</v>
@@ -1536,13 +1536,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
@@ -1551,16 +1551,16 @@
         <v>6</v>
       </c>
       <c r="BP4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>5.2</v>
@@ -1572,13 +1572,13 @@
         <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>1.91</v>
       </c>
       <c r="I5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1640,43 +1640,43 @@
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
         <v>14.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
         <v>13</v>
@@ -1688,7 +1688,7 @@
         <v>19</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>9.199999999999999</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="n">
         <v>23</v>
@@ -1706,13 +1706,13 @@
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1724,19 +1724,19 @@
         <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
         <v>12.5</v>
@@ -1745,76 +1745,76 @@
         <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="AY5" t="n">
         <v>15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC5" t="n">
         <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF5" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF5" t="n">
-        <v>9</v>
-      </c>
       <c r="BG5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.8</v>
+        <v>2.44</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8</v>
+        <v>2.46</v>
       </c>
       <c r="BT5" t="n">
         <v>4.6</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
         <v>10.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.44</v>
       </c>
       <c r="K6" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="L6" t="n">
         <v>1.65</v>
@@ -1906,7 +1906,7 @@
         <v>1.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
@@ -1915,7 +1915,7 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
         <v>1.37</v>
@@ -1924,16 +1924,16 @@
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
         <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
         <v>500</v>
@@ -1981,40 +1981,40 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.85</v>
+        <v>1.65</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>1.65</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AT6" t="n">
         <v>4.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.2</v>
+        <v>2.46</v>
       </c>
       <c r="AV6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.78</v>
       </c>
-      <c r="AW6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BB6" t="n">
         <v>1.84</v>
@@ -2023,16 +2023,16 @@
         <v>1.84</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
         <v>6.6</v>
@@ -2151,28 +2151,28 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S7" t="n">
         <v>1.76</v>
       </c>
       <c r="T7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -2184,22 +2184,22 @@
         <v>120</v>
       </c>
       <c r="Y7" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Z7" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA7" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AB7" t="n">
         <v>19</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AD7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AE7" t="n">
         <v>260</v>
@@ -2211,146 +2211,146 @@
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>100</v>
       </c>
       <c r="AJ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK7" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK7" t="n">
-        <v>14</v>
-      </c>
       <c r="AL7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM7" t="n">
         <v>260</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW7" t="n">
         <v>42</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AX7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>10</v>
-      </c>
       <c r="BC7" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
         <v>46</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BG7" t="n">
         <v>46</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BR7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT7" t="n">
         <v>13.5</v>
       </c>
       <c r="BU7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
         <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.21</v>
@@ -2405,55 +2405,55 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S8" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="T8" t="n">
         <v>1.35</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Y8" t="n">
         <v>38</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
@@ -2462,7 +2462,7 @@
         <v>50</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AH8" t="n">
         <v>13.5</v>
@@ -2471,7 +2471,7 @@
         <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
         <v>500</v>
@@ -2480,67 +2480,67 @@
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AN8" t="n">
         <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AU8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV8" t="n">
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB8" t="n">
         <v>27</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
         <v>5.8</v>
@@ -2552,59 +2552,59 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN8" t="n">
         <v>7.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CA8" t="n">
         <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="H9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.45</v>
@@ -2665,7 +2665,7 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
         <v>2.12</v>
@@ -2683,10 +2683,10 @@
         <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="X9" t="n">
         <v>12.5</v>
@@ -2698,7 +2698,7 @@
         <v>85</v>
       </c>
       <c r="AA9" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AB9" t="n">
         <v>6.6</v>
@@ -2734,13 +2734,13 @@
         <v>120</v>
       </c>
       <c r="AM9" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN9" t="n">
         <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
@@ -2749,10 +2749,10 @@
         <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
         <v>5.7</v>
@@ -2764,10 +2764,10 @@
         <v>30</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY9" t="n">
         <v>8.800000000000001</v>
@@ -2776,7 +2776,7 @@
         <v>27</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
@@ -2794,7 +2794,7 @@
         <v>9</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.25</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 04:28:19</t>
+          <t>2026-06-29 06:35:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,127 +857,127 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="G2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="I2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
         <v>5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC2" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AK2" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="n">
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
         <v>10.5</v>
@@ -986,37 +986,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AY2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF2" t="n">
         <v>60</v>
       </c>
-      <c r="BD2" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>50</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
@@ -1025,7 +1025,7 @@
         <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
         <v>7.6</v>
@@ -1034,43 +1034,43 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BP2" t="n">
         <v>55</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
         <v>4.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BW2" t="n">
         <v>7.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1111,91 +1111,91 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
         <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
         <v>260</v>
@@ -1213,103 +1213,103 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.91</v>
+        <v>2.58</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.82</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU3" t="n">
         <v>6</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.85</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.82</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1368,79 +1368,79 @@
         <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>9.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>36</v>
@@ -1449,61 +1449,61 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
         <v>160</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AP4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>14</v>
-      </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>8.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14</v>
       </c>
       <c r="BA4" t="n">
         <v>24</v>
@@ -1521,64 +1521,64 @@
         <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT4" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.2</v>
       </c>
       <c r="BU4" t="n">
         <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1619,43 +1619,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="I5" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
         <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
         <v>3.75</v>
@@ -1664,16 +1664,16 @@
         <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
         <v>8.800000000000001</v>
@@ -1682,13 +1682,13 @@
         <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB5" t="n">
         <v>19</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>9.199999999999999</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
         <v>23</v>
@@ -1712,7 +1712,7 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1724,25 +1724,25 @@
         <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP5" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AT5" t="n">
         <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
         <v>8.199999999999999</v>
@@ -1751,98 +1751,98 @@
         <v>15.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
         <v>10.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI5" t="n">
         <v>2.66</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.52</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BU5" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="K6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="P6" t="n">
         <v>1.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
         <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
         <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
         <v>970</v>
@@ -1999,25 +1999,25 @@
         <v>2.46</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AX6" t="n">
         <v>1.78</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BA6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.85</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.84</v>
       </c>
       <c r="BC6" t="n">
         <v>1.84</v>
@@ -2032,7 +2032,7 @@
         <v>1.86</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -2127,97 +2127,97 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="H7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.09</v>
       </c>
-      <c r="P7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.1</v>
-      </c>
       <c r="W7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X7" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="Y7" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="Z7" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AA7" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AB7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AD7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE7" t="n">
         <v>260</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK7" t="n">
         <v>13.5</v>
@@ -2229,106 +2229,106 @@
         <v>260</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV7" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AW7" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="BG7" t="n">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM7" t="n">
         <v>10.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO7" t="n">
         <v>4.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BS7" t="n">
         <v>7</v>
       </c>
       <c r="BT7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BV7" t="n">
         <v>60</v>
@@ -2337,20 +2337,20 @@
         <v>10.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -2384,52 +2384,52 @@
         <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q8" t="n">
         <v>1.33</v>
       </c>
       <c r="R8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="T8" t="n">
         <v>1.35</v>
       </c>
       <c r="U8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W8" t="n">
         <v>1.52</v>
@@ -2438,127 +2438,127 @@
         <v>120</v>
       </c>
       <c r="Y8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
         <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="AC8" t="n">
         <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH8" t="n">
         <v>13.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
         <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AQ8" t="n">
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AY8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN8" t="n">
         <v>7.2</v>
@@ -2570,13 +2570,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>9.6</v>
       </c>
       <c r="BT8" t="n">
         <v>6.6</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.45</v>
@@ -2674,37 +2674,37 @@
         <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
         <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="X9" t="n">
         <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA9" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AB9" t="n">
         <v>6.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>36</v>
@@ -2713,22 +2713,22 @@
         <v>190</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
         <v>180</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL9" t="n">
         <v>120</v>
@@ -2740,31 +2740,31 @@
         <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>5.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
         <v>6.8</v>
@@ -2773,13 +2773,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB9" t="n">
         <v>12</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2788,19 +2788,19 @@
         <v>40</v>
       </c>
       <c r="BE9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="n">
         <v>3.25</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9" t="n">
         <v>13</v>
@@ -2815,28 +2815,28 @@
         <v>11.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2848,17 +2848,17 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>24</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 06:35:13</t>
+          <t>2026-06-29 08:42:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K2" t="n">
         <v>5.6</v>
@@ -884,61 +884,61 @@
         <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AB2" t="n">
         <v>32</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AG2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
@@ -956,10 +956,10 @@
         <v>90</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>790</v>
       </c>
       <c r="AN2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO2" t="n">
         <v>5.5</v>
@@ -968,16 +968,16 @@
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS2" t="n">
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>10.5</v>
@@ -989,34 +989,34 @@
         <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AY2" t="n">
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BD2" t="n">
         <v>50</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
         <v>60</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
@@ -1025,52 +1025,52 @@
         <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BO2" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BR2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BT2" t="n">
         <v>4.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BV2" t="n">
         <v>8.4</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BY2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
         <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1141,7 +1141,7 @@
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
         <v>2.26</v>
@@ -1153,88 +1153,88 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
         <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>27</v>
       </c>
-      <c r="AI3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>32</v>
-      </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
         <v>180</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
@@ -1243,98 +1243,98 @@
         <v>36</v>
       </c>
       <c r="AX3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.58</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
         <v>10</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>9.4</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="I4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.34</v>
@@ -1389,55 +1389,55 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
         <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
         <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>9.4</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1446,7 +1446,7 @@
         <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
@@ -1455,25 +1455,25 @@
         <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
         <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AO4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
         <v>10.5</v>
@@ -1482,46 +1482,46 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB4" t="n">
         <v>46</v>
       </c>
       <c r="BC4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BD4" t="n">
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG4" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN4" t="n">
         <v>7.6</v>
@@ -1554,31 +1554,31 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU4" t="n">
         <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>5.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.75</v>
@@ -1640,13 +1640,13 @@
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
         <v>1.87</v>
@@ -1661,49 +1661,49 @@
         <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W5" t="n">
         <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
         <v>19</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="n">
         <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
@@ -1712,7 +1712,7 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1724,10 +1724,10 @@
         <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.2</v>
@@ -1736,52 +1736,52 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY5" t="n">
         <v>15.5</v>
       </c>
-      <c r="AT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BC5" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BD5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BI5" t="n">
         <v>2.66</v>
@@ -1790,34 +1790,34 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
         <v>8.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU5" t="n">
         <v>3.9</v>
@@ -1826,23 +1826,23 @@
         <v>14</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -1873,61 +1873,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="K6" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="N6" t="n">
         <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P6" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y6" t="n">
         <v>500</v>
@@ -1978,19 +1978,19 @@
         <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AT6" t="n">
         <v>4.4</v>
@@ -1999,40 +1999,40 @@
         <v>2.46</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -2127,79 +2127,79 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.28</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.31</v>
-      </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="S7" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
         <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="X7" t="n">
-        <v>240</v>
+        <v>70</v>
       </c>
       <c r="Y7" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA7" t="n">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AB7" t="n">
         <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE7" t="n">
         <v>260</v>
@@ -2211,82 +2211,82 @@
         <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK7" t="n">
         <v>13.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM7" t="n">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY7" t="n">
         <v>11</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AZ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BD7" t="n">
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="BG7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="n">
         <v>7.2</v>
@@ -2295,16 +2295,16 @@
         <v>5.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
         <v>8</v>
       </c>
       <c r="BL7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
         <v>4.9</v>
@@ -2313,44 +2313,44 @@
         <v>4.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT7" t="n">
         <v>15.5</v>
       </c>
-      <c r="BS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BU7" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ7" t="n">
         <v>6.2</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.2</v>
@@ -2405,46 +2405,46 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U8" t="n">
         <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
         <v>120</v>
       </c>
       <c r="Y8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
         <v>29</v>
@@ -2456,61 +2456,61 @@
         <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AG8" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>13.5</v>
       </c>
       <c r="AI8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK8" t="n">
         <v>24</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>500</v>
-      </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AM8" t="n">
         <v>44</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AP8" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
         <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
       </c>
       <c r="AU8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX8" t="n">
         <v>25</v>
@@ -2525,7 +2525,7 @@
         <v>17.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BC8" t="n">
         <v>21</v>
@@ -2537,10 +2537,10 @@
         <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="n">
         <v>6.2</v>
@@ -2552,7 +2552,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2570,10 +2570,10 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS8" t="n">
         <v>8.800000000000001</v>
@@ -2588,7 +2588,7 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>18</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>
@@ -2641,25 +2641,25 @@
         <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
@@ -2668,7 +2668,7 @@
         <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -2677,16 +2677,16 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
         <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="X9" t="n">
         <v>12.5</v>
@@ -2698,7 +2698,7 @@
         <v>75</v>
       </c>
       <c r="AA9" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AB9" t="n">
         <v>6.6</v>
@@ -2707,7 +2707,7 @@
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
         <v>190</v>
@@ -2719,7 +2719,7 @@
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
         <v>180</v>
@@ -2728,10 +2728,10 @@
         <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL9" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
         <v>240</v>
@@ -2740,19 +2740,19 @@
         <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
         <v>5.7</v>
@@ -2764,10 +2764,10 @@
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>8.800000000000001</v>
@@ -2776,7 +2776,7 @@
         <v>26</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
         <v>12</v>
@@ -2785,80 +2785,80 @@
         <v>16</v>
       </c>
       <c r="BD9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
         <v>2.68</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP9" t="n">
         <v>11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR9" t="n">
         <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 08:42:13</t>
+          <t>2026-06-29 10:49:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.6</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.49</v>
+        <v>1.07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3</v>
+        <v>17.5</v>
       </c>
       <c r="K2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V2" t="n">
+        <v>15</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA2" t="n">
         <v>5.6</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X2" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AB2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AJ2" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AM2" t="n">
-        <v>790</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BD2" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="H3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>360</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>360</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AU3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="n">
         <v>80</v>
       </c>
-      <c r="AP3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>28</v>
-      </c>
       <c r="BB3" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
         <v>22</v>
       </c>
       <c r="BD3" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>180</v>
       </c>
       <c r="BF3" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="H4" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF4" t="n">
         <v>23</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>36</v>
       </c>
       <c r="AG4" t="n">
         <v>16</v>
       </c>
       <c r="AH4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>16</v>
       </c>
-      <c r="AI4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="BK4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>730</v>
+      </c>
+      <c r="BM4" t="n">
         <v>12</v>
       </c>
-      <c r="AP4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BN4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP4" t="n">
         <v>46</v>
       </c>
-      <c r="BC4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BR4" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
         <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
         <v>4.7</v>
       </c>
-      <c r="G5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.02</v>
-      </c>
       <c r="V5" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO5" t="n">
         <v>25</v>
       </c>
-      <c r="AB5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>16</v>
-      </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AY5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BC5" t="n">
         <v>42</v>
       </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BE5" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="BF5" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BX5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA5" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="J6" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
         <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Q6" t="n">
         <v>3.3</v>
@@ -1915,16 +1915,16 @@
         <v>7.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
         <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
         <v>9.800000000000001</v>
@@ -1987,28 +1987,28 @@
         <v>1.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AS6" t="n">
         <v>1.94</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AU6" t="n">
         <v>2.46</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AW6" t="n">
         <v>1.95</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.4</v>
+        <v>1.88</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.6</v>
+        <v>1.85</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.92</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -2127,88 +2127,88 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.08</v>
       </c>
-      <c r="P7" t="n">
+      <c r="W7" t="n">
         <v>4.7</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="X7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y7" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="Z7" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AA7" t="n">
         <v>410</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC7" t="n">
         <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AE7" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -2229,34 +2229,34 @@
         <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AO7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>12</v>
       </c>
-      <c r="AS7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AT7" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AV7" t="n">
         <v>32</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
         <v>12</v>
@@ -2283,16 +2283,16 @@
         <v>30</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="BG7" t="n">
         <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
@@ -2304,10 +2304,10 @@
         <v>75</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO7" t="n">
         <v>4.2</v>
@@ -2319,38 +2319,38 @@
         <v>6</v>
       </c>
       <c r="BR7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT7" t="n">
         <v>16</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>15.5</v>
       </c>
       <c r="BU7" t="n">
         <v>6.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>48</v>
       </c>
       <c r="BY7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
         <v>2.4</v>
@@ -2399,34 +2399,34 @@
         <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="V8" t="n">
         <v>1.67</v>
@@ -2435,25 +2435,25 @@
         <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
         <v>22</v>
@@ -2462,7 +2462,7 @@
         <v>32</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH8" t="n">
         <v>13.5</v>
@@ -2471,49 +2471,49 @@
         <v>22</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
         <v>24</v>
       </c>
       <c r="AL8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>24</v>
       </c>
-      <c r="AM8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>22</v>
-      </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AT8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY8" t="n">
         <v>13.5</v>
@@ -2522,67 +2522,67 @@
         <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BB8" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BC8" t="n">
         <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
         <v>7.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>8.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2591,20 +2591,20 @@
         <v>7.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BY8" t="n">
         <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>
@@ -2635,85 +2635,85 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="H9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA9" t="n">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="n">
         <v>190</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
@@ -2725,22 +2725,22 @@
         <v>180</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
@@ -2749,25 +2749,25 @@
         <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>5.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY9" t="n">
         <v>8.800000000000001</v>
@@ -2779,7 +2779,7 @@
         <v>11.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2788,77 +2788,77 @@
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>10</v>
-      </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CA9" t="n">
         <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-29 10:49:32</t>
+          <t>2026-06-29 12:56:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Club Lujan</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.76</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>1.13</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>60</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>6.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>1.95</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.56</v>
+        <v>50</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.15</v>
+        <v>100</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.2</v>
+        <v>28</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.52</v>
+        <v>15</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.96</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.25</v>
+        <v>65</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.4</v>
+        <v>32</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.6</v>
+        <v>100</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>1.33</v>
+        <v>34</v>
       </c>
       <c r="H3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="I3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J3" t="n">
         <v>10.5</v>
       </c>
-      <c r="J3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="R3" t="n">
         <v>2.52</v>
       </c>
       <c r="S3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="W3" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>300</v>
+        <v>7.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>15.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>60</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.88</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="n">
-        <v>100</v>
+        <v>3.65</v>
       </c>
       <c r="AP3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AU3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AV3" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>75</v>
+        <v>7.2</v>
       </c>
       <c r="AX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>14</v>
       </c>
-      <c r="AY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>30</v>
-      </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.7</v>
+        <v>90</v>
       </c>
       <c r="BG3" t="n">
-        <v>25</v>
+        <v>3.45</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,498 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Democrata GV</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Ivinhema FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.68</v>
+        <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC4" t="n">
         <v>10.5</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X4" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AD4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH4" t="n">
         <v>29</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AI4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>790</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR4" t="n">
         <v>29</v>
       </c>
-      <c r="AA4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ4" t="n">
+      <c r="BS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT4" t="n">
         <v>12</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
         <v>6</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-29 15:03:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Brazilian Serie D</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Democrata GV</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ivinhema FC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>790</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>330</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-29 15:03:30</t>
+          <t>2026-06-29 17:10:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Brazilian Serie D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,752 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Democrata GV</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Ivinhema FC</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42</v>
-      </c>
-      <c r="I2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>13</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>10</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W2" t="n">
-        <v>8.800000000000001</v>
+        <v>2.78</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
       </c>
       <c r="AH2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK2" t="n">
         <v>21</v>
       </c>
-      <c r="AI2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6.6</v>
       </c>
-      <c r="AL2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>28</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="BE2" t="n">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.81</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-29 17:10:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Icelandic Urvalsdeild</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>16:15:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>IA Akranes</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fram</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>30</v>
-      </c>
-      <c r="G3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-29 17:10:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Brazilian Serie D</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Democrata GV</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ivinhema FC</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>790</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-29 17:10:34</t>
+          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Brazilian Serie D</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Democrata GV</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Ivinhema FC</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>410</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>390</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>150</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>170</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>200</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>940</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>910</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>90</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>950</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>55</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-29 19:17:42</t>
         </is>
       </c>
     </row>
